--- a/data/scenario_summary.xlsx
+++ b/data/scenario_summary.xlsx
@@ -1067,7 +1067,7 @@
         <v>-67.07202876067853</v>
       </c>
       <c r="F20" t="n">
-        <v>-81.23724873861646</v>
+        <v>-81.23724863135857</v>
       </c>
       <c r="G20" t="n">
         <v>-2.144214888472146</v>
@@ -1101,7 +1101,7 @@
         <v>-46.45852320436207</v>
       </c>
       <c r="F21" t="n">
-        <v>-58.0921287899663</v>
+        <v>-58.08830734163011</v>
       </c>
       <c r="G21" t="n">
         <v>-48.4558812483103</v>
